--- a/data/trans_camb/P59A-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P59A-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 5,61</t>
+          <t>-0,98; 5,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,0; 3,78</t>
+          <t>-2,5; 4,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 3,2</t>
+          <t>-4,43; 4,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 6,08</t>
+          <t>-2,81; 5,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 8,86</t>
+          <t>-0,71; 8,31</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 3,3</t>
+          <t>-6,79; 3,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,97; 4,52</t>
+          <t>-0,87; 4,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 5,09</t>
+          <t>-0,39; 5,1</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 1,5</t>
+          <t>-4,84; 1,6</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,79; 137,87</t>
+          <t>-15,42; 129,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-40,19; 90,53</t>
+          <t>-35,51; 98,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-67,77; 80,0</t>
+          <t>-66,22; 92,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-21,24; 75,66</t>
+          <t>-24,99; 69,64</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 116,41</t>
+          <t>-6,23; 105,54</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-61,4; 37,88</t>
+          <t>-58,87; 43,1</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-11,58; 68,77</t>
+          <t>-9,98; 73,48</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 75,37</t>
+          <t>-4,53; 78,28</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-55,77; 25,24</t>
+          <t>-56,56; 24,61</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 4,51</t>
+          <t>-6,96; 4,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,04; 14,57</t>
+          <t>1,85; 14,73</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 14,67</t>
+          <t>-1,45; 14,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 10,65</t>
+          <t>-5,23; 10,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 10,39</t>
+          <t>-4,25; 10,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-16,34; 6,4</t>
+          <t>-17,65; 5,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 4,63</t>
+          <t>-4,23; 5,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,55; 11,0</t>
+          <t>1,89; 11,34</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 7,67</t>
+          <t>-6,3; 7,95</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-27,08; 21,89</t>
+          <t>-25,73; 20,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,21; 71,06</t>
+          <t>5,99; 67,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 66,61</t>
+          <t>-5,57; 68,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-16,13; 45,16</t>
+          <t>-17,63; 44,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 43,93</t>
+          <t>-13,37; 47,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-52,88; 25,17</t>
+          <t>-56,51; 22,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-16,15; 19,79</t>
+          <t>-15,46; 21,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5,38; 47,27</t>
+          <t>6,96; 49,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-24,07; 31,99</t>
+          <t>-23,52; 32,71</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,5; 19,44</t>
+          <t>1,24; 20,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,64; 20,93</t>
+          <t>3,9; 20,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>9,09; 25,95</t>
+          <t>8,85; 25,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8,41; 29,83</t>
+          <t>9,13; 30,25</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,42; 23,19</t>
+          <t>5,88; 23,13</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,63; 28,57</t>
+          <t>11,32; 28,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,82; 22,48</t>
+          <t>7,83; 21,89</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,49; 20,03</t>
+          <t>7,67; 20,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>11,77; 24,62</t>
+          <t>13,26; 24,68</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,11; 250,64</t>
+          <t>5,76; 257,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>20,16; 281,96</t>
+          <t>19,41; 288,68</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49,37; 357,82</t>
+          <t>48,26; 343,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46,27; 352,03</t>
+          <t>49,82; 366,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30,53; 303,94</t>
+          <t>31,25; 290,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>66,87; 347,0</t>
+          <t>59,03; 370,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>50,75; 253,41</t>
+          <t>53,38; 259,96</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>46,03; 231,96</t>
+          <t>48,95; 233,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>70,23; 282,69</t>
+          <t>78,79; 277,33</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-12,45; 9,87</t>
+          <t>-11,44; 11,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,56; 2,68</t>
+          <t>-16,95; 3,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 1,43</t>
+          <t>-18,05; 1,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,16; 13,52</t>
+          <t>1,21; 13,55</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,79; 14,57</t>
+          <t>2,82; 14,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,82; 19,71</t>
+          <t>9,72; 19,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 9,65</t>
+          <t>-2,65; 10,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 7,45</t>
+          <t>-4,27; 7,1</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 9,15</t>
+          <t>-1,99; 9,05</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-51,45; 74,63</t>
+          <t>-45,9; 99,33</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-64,4; 23,54</t>
+          <t>-65,25; 27,7</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-62,56; 14,86</t>
+          <t>-65,14; 15,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-34,45; —</t>
+          <t>-16,29; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>21,37; —</t>
+          <t>19,09; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>134,56; —</t>
+          <t>149,31; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-25,1; 143,34</t>
+          <t>-21,69; 172,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,47; 117,24</t>
+          <t>-30,63; 110,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-12,05; 140,63</t>
+          <t>-14,22; 141,89</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-13,57; 11,74</t>
+          <t>-14,11; 10,77</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,97; 15,37</t>
+          <t>-10,5; 15,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-12,68; 7,96</t>
+          <t>-13,78; 8,26</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,18; 16,22</t>
+          <t>1,53; 15,95</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 6,43</t>
+          <t>-3,25; 6,48</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 7,87</t>
+          <t>-1,11; 8,05</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 11,88</t>
+          <t>-1,98; 11,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 8,0</t>
+          <t>-3,34; 8,1</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 7,29</t>
+          <t>-3,44; 7,0</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-73,17; 211,84</t>
+          <t>-76,2; 158,71</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-46,34; 244,34</t>
+          <t>-50,73; 232,27</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-60,87; 139,82</t>
+          <t>-58,56; 140,42</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-19,13; 1283,76</t>
+          <t>-19,9; 1386,52</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-74,79; 702,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-21,99; 754,6</t>
+          <t>-25,81; 787,21</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-23,72; 304,76</t>
+          <t>-25,3; 316,57</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-42,29; 230,03</t>
+          <t>-35,97; 213,7</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-29,07; 196,73</t>
+          <t>-29,14; 191,18</t>
         </is>
       </c>
     </row>
@@ -1757,22 +1757,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 10,69</t>
+          <t>-4,81; 10,08</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,61; 10,65</t>
+          <t>-2,97; 10,64</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 10,53</t>
+          <t>-2,01; 10,45</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,67; 7,36</t>
+          <t>0,66; 6,91</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1782,22 +1782,22 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,76</t>
+          <t>1,22; 4,5</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,46; 6,43</t>
+          <t>0,47; 6,3</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 4,35</t>
+          <t>-0,14; 3,99</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,88; 6,02</t>
+          <t>2,03; 6,16</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 0,0</t>
+          <t>-9,69; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 4,4</t>
+          <t>-5,6; 4,44</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 9,11</t>
+          <t>-1,87; 8,96</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,09</t>
+          <t>0,0; 2,67</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,26</t>
+          <t>0,0; 4,28</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,46</t>
+          <t>0,21; 1,5</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,33</t>
+          <t>-1,25; 1,33</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 2,57</t>
+          <t>-0,72; 2,98</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0,09; 2,85</t>
+          <t>-0,13; 2,82</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-55,83; —</t>
+          <t>-56,26; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-42,38; —</t>
+          <t>-32,58; —</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 4,43</t>
+          <t>-1,26; 4,41</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,94; 6,69</t>
+          <t>1,02; 6,86</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 5,04</t>
+          <t>-0,73; 5,32</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,58</t>
+          <t>1,47; 6,43</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,44; 6,24</t>
+          <t>1,35; 6,41</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,22; 5,29</t>
+          <t>0,26; 5,03</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,84</t>
+          <t>0,97; 4,89</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,52</t>
+          <t>1,98; 5,88</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,58</t>
+          <t>0,35; 4,53</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-9,03; 35,88</t>
+          <t>-8,68; 35,19</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>6,01; 54,02</t>
+          <t>6,58; 55,96</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 42,66</t>
+          <t>-5,0; 42,05</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>12,17; 73,14</t>
+          <t>13,07; 70,5</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>12,29; 69,16</t>
+          <t>9,82; 69,39</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,15; 58,72</t>
+          <t>2,26; 55,72</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>7,45; 43,53</t>
+          <t>8,12; 46,17</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>14,71; 50,55</t>
+          <t>15,87; 55,81</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>4,71; 41,67</t>
+          <t>2,5; 41,15</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P59A-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P59A-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,11</t>
+          <t>-0,3</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,15</t>
+          <t>-2,49</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,78</t>
+          <t>-1,41</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 5,86</t>
+          <t>-1,4; 5,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 4,11</t>
+          <t>-2,8; 4,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 4,07</t>
+          <t>-4,14; 4,45</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 5,93</t>
+          <t>-2,48; 5,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 8,31</t>
+          <t>-0,72; 8,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 3,49</t>
+          <t>-6,78; 2,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 4,72</t>
+          <t>-1,01; 4,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 5,1</t>
+          <t>-0,74; 4,77</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 1,6</t>
+          <t>-4,47; 1,75</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-19,23%</t>
+          <t>-5,27%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-21,7%</t>
+          <t>-25,15%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-22,86%</t>
+          <t>-18,09%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,42; 129,33</t>
+          <t>-20,87; 128,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-35,51; 98,6</t>
+          <t>-38,43; 100,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-66,22; 92,97</t>
+          <t>-60,32; 103,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-24,99; 69,64</t>
+          <t>-21,93; 74,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-6,23; 105,54</t>
+          <t>-7,14; 104,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-58,87; 43,1</t>
+          <t>-58,55; 41,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-9,98; 73,48</t>
+          <t>-11,47; 64,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 78,28</t>
+          <t>-8,96; 72,26</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-56,56; 24,61</t>
+          <t>-50,9; 26,51</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,21</t>
+          <t>4,69</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,39</t>
+          <t>2,69</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1,77</t>
+          <t>4,03</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,96; 4,34</t>
+          <t>-6,95; 4,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 14,73</t>
+          <t>2,24; 14,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 14,61</t>
+          <t>-2,68; 12,14</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 10,63</t>
+          <t>-4,87; 10,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 10,93</t>
+          <t>-4,65; 10,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-17,65; 5,95</t>
+          <t>-5,27; 9,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 5,0</t>
+          <t>-4,9; 4,7</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,89; 11,34</t>
+          <t>1,05; 10,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 7,95</t>
+          <t>-1,29; 9,67</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-12,17%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>15,72%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-25,73; 20,04</t>
+          <t>-25,05; 21,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>5,99; 67,62</t>
+          <t>7,81; 70,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 68,44</t>
+          <t>-10,72; 56,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,63; 44,94</t>
+          <t>-15,08; 45,8</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-13,37; 47,0</t>
+          <t>-14,14; 42,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-56,51; 22,85</t>
+          <t>-16,6; 39,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-15,46; 21,33</t>
+          <t>-17,35; 20,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,96; 49,37</t>
+          <t>3,37; 45,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-23,52; 32,71</t>
+          <t>-4,71; 40,33</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17,64</t>
+          <t>18,65</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,3</t>
+          <t>20,61</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>18,85</t>
+          <t>19,54</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,24; 20,02</t>
+          <t>1,68; 20,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,9; 20,95</t>
+          <t>4,55; 21,28</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,85; 25,57</t>
+          <t>10,47; 26,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,13; 30,25</t>
+          <t>9,01; 29,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,88; 23,13</t>
+          <t>4,87; 23,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,32; 28,11</t>
+          <t>11,87; 27,65</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,83; 21,89</t>
+          <t>7,89; 21,4</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>7,67; 20,06</t>
+          <t>7,32; 20,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,26; 24,68</t>
+          <t>13,5; 24,86</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>151,63%</t>
+          <t>160,3%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>163,08%</t>
+          <t>165,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>156,73%</t>
+          <t>162,5%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,76; 257,9</t>
+          <t>5,53; 263,67</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,41; 288,68</t>
+          <t>22,53; 288,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48,26; 343,53</t>
+          <t>54,4; 369,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>49,82; 366,0</t>
+          <t>48,59; 384,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31,25; 290,24</t>
+          <t>23,59; 277,56</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>59,03; 370,89</t>
+          <t>65,0; 352,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>53,38; 259,96</t>
+          <t>53,28; 249,5</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>48,95; 233,16</t>
+          <t>45,09; 218,42</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>78,79; 277,33</t>
+          <t>85,23; 278,44</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-6,84</t>
+          <t>-6,72</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,03</t>
+          <t>15,72</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,36</t>
+          <t>4,79</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-11,44; 11,32</t>
+          <t>-12,44; 10,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-16,95; 3,37</t>
+          <t>-17,12; 3,72</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-18,05; 1,76</t>
+          <t>-19,05; 1,78</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,21; 13,55</t>
+          <t>1,43; 14,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 14,73</t>
+          <t>3,22; 13,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,72; 19,89</t>
+          <t>10,67; 20,42</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 10,82</t>
+          <t>-3,45; 10,25</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,27; 7,1</t>
+          <t>-3,97; 7,95</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 9,05</t>
+          <t>-0,77; 9,88</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-36,46%</t>
+          <t>-35,86%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>780,36%</t>
+          <t>816,18%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>44,68%</t>
+          <t>49,08%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-45,9; 99,33</t>
+          <t>-51,0; 78,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-65,25; 27,7</t>
+          <t>-64,03; 33,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-65,14; 15,1</t>
+          <t>-65,02; 20,89</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-16,29; —</t>
+          <t>-35,53; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,09; —</t>
+          <t>18,51; —</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>149,31; —</t>
+          <t>158,6; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,69; 172,94</t>
+          <t>-27,39; 150,9</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-30,63; 110,16</t>
+          <t>-31,36; 131,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 141,89</t>
+          <t>-6,6; 157,63</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-1,3</t>
+          <t>-0,97</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,24</t>
+          <t>4,56</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>2,79</t>
+          <t>3,06</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 10,77</t>
+          <t>-14,95; 12,11</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-10,5; 15,01</t>
+          <t>-9,2; 14,58</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-13,78; 8,26</t>
+          <t>-12,84; 8,01</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,53; 15,95</t>
+          <t>0,94; 16,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 6,48</t>
+          <t>-3,58; 6,29</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 8,05</t>
+          <t>-0,58; 8,83</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 11,84</t>
+          <t>-2,34; 11,64</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 8,1</t>
+          <t>-3,38; 8,06</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 7,0</t>
+          <t>-2,63; 7,38</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-9,67%</t>
+          <t>-7,21%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>131,54%</t>
+          <t>141,69%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>44,03%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-76,2; 158,71</t>
+          <t>-74,49; 189,59</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-50,73; 232,27</t>
+          <t>-49,74; 245,96</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-58,56; 140,42</t>
+          <t>-55,88; 128,91</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-19,9; 1386,52</t>
+          <t>-24,97; 1261,4</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-70,22; 696,19</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-25,81; 787,21</t>
+          <t>-17,92; 799,77</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-25,3; 316,57</t>
+          <t>-29,34; 268,46</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-35,97; 213,7</t>
+          <t>-33,44; 210,64</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-29,14; 191,18</t>
+          <t>-26,01; 181,42</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5,49</t>
+          <t>6,87</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2,44</t>
+          <t>2,38</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3,92</t>
+          <t>4,44</t>
         </is>
       </c>
     </row>
@@ -1757,22 +1757,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 10,08</t>
+          <t>-4,85; 10,03</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 10,64</t>
+          <t>-2,8; 10,42</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 10,45</t>
+          <t>-0,96; 12,68</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,91</t>
+          <t>0,67; 7,92</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1782,22 +1782,22 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,5</t>
+          <t>1,04; 4,11</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,47; 6,3</t>
+          <t>0,47; 6,79</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 3,99</t>
+          <t>-0,5; 4,07</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2,03; 6,16</t>
+          <t>2,15; 6,68</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>244,61%</t>
+          <t>305,83%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>787,68%</t>
+          <t>891,14%</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3,91</t>
+          <t>4,08</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,61</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1,45</t>
+          <t>1,62</t>
         </is>
       </c>
     </row>
@@ -1973,32 +1973,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-9,69; 0,0</t>
+          <t>-9,59; 0,0</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 4,44</t>
+          <t>-5,81; 3,81</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 8,96</t>
+          <t>-1,61; 9,49</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,67</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,28</t>
+          <t>0,0; 4,37</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,5</t>
+          <t>0,3; 1,93</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -2008,12 +2008,12 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 2,98</t>
+          <t>-0,96; 2,79</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 2,82</t>
+          <t>0,22; 3,11</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>139,99%</t>
+          <t>146,14%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>224,33%</t>
+          <t>250,25%</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-56,26; —</t>
+          <t>-44,1; —</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-32,58; —</t>
+          <t>-25,76; —</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2,18</t>
+          <t>2,62</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,84</t>
+          <t>3,54</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2,52</t>
+          <t>3,1</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 4,41</t>
+          <t>-1,2; 4,45</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>1,02; 6,86</t>
+          <t>0,95; 6,57</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 5,32</t>
+          <t>-0,08; 5,7</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,47; 6,43</t>
+          <t>1,18; 6,53</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,35; 6,41</t>
+          <t>1,48; 6,26</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,26; 5,03</t>
+          <t>1,19; 5,83</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,89</t>
+          <t>0,82; 4,62</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1,98; 5,88</t>
+          <t>1,93; 5,64</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,53</t>
+          <t>1,29; 4,95</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>26,07%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-8,68; 35,19</t>
+          <t>-8,1; 36,54</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>6,58; 55,96</t>
+          <t>6,22; 54,06</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 42,05</t>
+          <t>-1,15; 46,8</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>13,07; 70,5</t>
+          <t>9,89; 71,14</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>9,82; 69,39</t>
+          <t>12,48; 68,26</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,26; 55,72</t>
+          <t>10,21; 66,18</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>8,12; 46,17</t>
+          <t>6,21; 41,56</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>15,87; 55,81</t>
+          <t>15,01; 51,18</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>2,5; 41,15</t>
+          <t>10,47; 45,55</t>
         </is>
       </c>
     </row>
